--- a/outputs/etf_trend_strategy/threshold_0.9/backtests/window_20/return_vol/post_rank_positive_return/staggered_5d/close/close_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.9/backtests/window_20/return_vol/post_rank_positive_return/staggered_5d/close/close_annual_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="annual_metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'annual_metrics'!$A$1:$H$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'annual_metrics'!$A$1:$N$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -462,17 +462,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -488,30 +494,60 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>基准收益</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>超额收益</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>年化波动</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>跟踪误差</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Sharpe</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Sortino</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>信息比率</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>策略最大回撤</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>基准最大回撤</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>超额最大回撤</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Calmar</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>年化换手率（单边）</t>
         </is>
@@ -527,21 +563,39 @@
         <v>0.07965302357984894</v>
       </c>
       <c r="C2" s="3" t="n">
+        <v>-0.02176047699359285</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0.1036693960818202</v>
+      </c>
+      <c r="E2" s="3" t="n">
         <v>0.2763498197505358</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="F2" s="3" t="n">
+        <v>0.2309178587376848</v>
+      </c>
+      <c r="G2" s="4" t="n">
         <v>0.3970315816653889</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="H2" s="4" t="n">
         <v>0.5778686857493104</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="I2" s="4" t="n">
+        <v>0.5773984643826308</v>
+      </c>
+      <c r="J2" s="3" t="n">
         <v>0.1721981489272064</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="K2" s="3" t="n">
+        <v>0.1506490308477421</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>0.1582930413519892</v>
+      </c>
+      <c r="M2" s="4" t="n">
         <v>0.5253674031758705</v>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="N2" s="5" t="n">
         <v>25.7019392926341</v>
       </c>
     </row>
@@ -555,21 +609,39 @@
         <v>-0.2566493764401636</v>
       </c>
       <c r="C3" s="3" t="n">
+        <v>-0.2255774308756096</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>-0.04012272731111988</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>0.2212329121256089</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="F3" s="3" t="n">
+        <v>0.1602335587573368</v>
+      </c>
+      <c r="G3" s="4" t="n">
         <v>-1.351793707933265</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="H3" s="4" t="n">
         <v>-1.732509665007366</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="I3" s="4" t="n">
+        <v>-0.2483095209083244</v>
+      </c>
+      <c r="J3" s="3" t="n">
         <v>0.2887112358391767</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="K3" s="3" t="n">
+        <v>0.2845881262232945</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0.1679315393948687</v>
+      </c>
+      <c r="M3" s="4" t="n">
         <v>-0.9203107172147805</v>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="N3" s="5" t="n">
         <v>24.18824178981269</v>
       </c>
     </row>
@@ -583,21 +655,39 @@
         <v>-0.1164638431672435</v>
       </c>
       <c r="C4" s="3" t="n">
+        <v>-0.1141699148043651</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>-0.002589580554120396</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>0.1979332036935636</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="F4" s="3" t="n">
+        <v>0.153827972234518</v>
+      </c>
+      <c r="G4" s="4" t="n">
         <v>-0.6279545823269445</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="H4" s="4" t="n">
         <v>-0.893509706107437</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="I4" s="4" t="n">
+        <v>0.04996067329854526</v>
+      </c>
+      <c r="J4" s="3" t="n">
         <v>0.2526977709835553</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="K4" s="3" t="n">
+        <v>0.2177913835362562</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0.1359912690913769</v>
+      </c>
+      <c r="M4" s="4" t="n">
         <v>-0.4787262150663532</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="N4" s="5" t="n">
         <v>25.57227301265212</v>
       </c>
     </row>
@@ -611,21 +701,39 @@
         <v>-0.004440582040153407</v>
       </c>
       <c r="C5" s="3" t="n">
+        <v>0.1298071537204202</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>-0.1188235844661645</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>0.2525380180327504</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="F5" s="3" t="n">
+        <v>0.1304837871815858</v>
+      </c>
+      <c r="G5" s="4" t="n">
         <v>0.04651078739312123</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>0.07717501552095292</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="I5" s="4" t="n">
+        <v>-0.9664737339150041</v>
+      </c>
+      <c r="J5" s="3" t="n">
         <v>0.2524105346054599</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="K5" s="3" t="n">
+        <v>0.1515696200238076</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>0.1980954241665657</v>
+      </c>
+      <c r="M5" s="4" t="n">
         <v>-0.01831798471432298</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="N5" s="5" t="n">
         <v>26.70458330844664</v>
       </c>
     </row>
@@ -639,54 +747,90 @@
         <v>0.2124726119891305</v>
       </c>
       <c r="C6" s="3" t="n">
+        <v>0.2243203183030871</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>-0.009676966180205526</v>
+      </c>
+      <c r="E6" s="3" t="n">
         <v>0.2313710718330021</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="F6" s="3" t="n">
+        <v>0.1339621596909893</v>
+      </c>
+      <c r="G6" s="4" t="n">
         <v>0.9150788593358509</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>1.319420656629966</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="I6" s="4" t="n">
+        <v>0.01942681320442305</v>
+      </c>
+      <c r="J6" s="3" t="n">
         <v>0.1517975608147537</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="K6" s="3" t="n">
+        <v>0.1188658802983931</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0.1071935635814688</v>
+      </c>
+      <c r="M6" s="4" t="n">
         <v>1.45690943025251</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="N6" s="5" t="n">
         <v>29.39925348460858</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026年截至07-31</t>
+          <t>2026年截至07-30</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.1801408215705909</v>
+        <v>0.1848036099616015</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.3340432927357005</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>1.021714239195194</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>1.426293098247805</v>
+        <v>-0.01504143451691176</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0.202896904988582</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.3351811463945258</v>
       </c>
       <c r="F7" s="3" t="n">
+        <v>0.2148493863269766</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>1.047387076892545</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>1.462194849544718</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>1.70998006599036</v>
+      </c>
+      <c r="J7" s="3" t="n">
         <v>0.1780554182416551</v>
       </c>
-      <c r="G7" s="4" t="n">
-        <v>1.96705330806174</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>24.57793585014834</v>
+      <c r="K7" s="3" t="n">
+        <v>0.127969093077366</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0.09090676987567592</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>2.038494019378844</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>24.65392947437687</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H7"/>
+  <autoFilter ref="A1:N7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>